--- a/public/data/heberges.xlsx
+++ b/public/data/heberges.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pcazenp5\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94F1A56-C272-437E-82D0-C9BF31386CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8C06EED-8AEE-47BF-832B-078516E0284D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{2D276C0A-BE79-432A-ADD8-ECF238F42A1B}"/>
   </bookViews>
